--- a/design/docs/components_list.xlsx
+++ b/design/docs/components_list.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="174">
   <si>
     <t>Confirmado</t>
   </si>
@@ -393,115 +393,442 @@
     <t>Herramientas mecánicas</t>
   </si>
   <si>
-    <t>Arma</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Confirmado</t>
+    </r>
   </si>
   <si>
-    <t>Fabricable</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Nombre</t>
+    </r>
   </si>
   <si>
-    <t>Necesario</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Descripción</t>
+    </r>
   </si>
   <si>
-    <t>Inicial en bolsa saqueo</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Arma</t>
+    </r>
   </si>
   <si>
-    <t>En App</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Fabricable</t>
+    </r>
   </si>
   <si>
-    <t>Basura aprovechable</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Necesario</t>
+    </r>
   </si>
   <si>
-    <t>0 (en dado de búsqueda)</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Inicial en bolsa saqueo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>En App</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Basura aprovechable</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>0 (en dado de búsqueda)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Vendas</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Desinfectante</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Botiquín</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t xml:space="preserve">Cura 3 heridas a un personaje </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>S</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Vendas, desinfectante, aguja</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Palo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Cuchillo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Cinta aislante</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Lanza</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Palo, cuchillo, cinta aislante</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Pilas</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Linterna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Palanca</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Para entrar en sitios</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Comida</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Agua</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Cuerda</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Arco</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>2</t>
+    </r>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Vendas</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Flecha</t>
+    </r>
   </si>
   <si>
-    <t>Desinfectante</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Solo si tienes arco. Se pueden recuperar cuando finaliza el combate</t>
+    </r>
   </si>
   <si>
-    <t>Botiquín</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Saco de dormir</t>
+    </r>
   </si>
   <si>
-    <t xml:space="preserve">Cura 3 heridas a un personaje </t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Evita heridas si no duermes en un enclave principal?</t>
+    </r>
   </si>
   <si>
-    <t>Vendas, desinfectante, aguja</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Pico escalada</t>
+    </r>
   </si>
   <si>
-    <t>Palo</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Caña de pescar</t>
+    </r>
   </si>
   <si>
-    <t>Cuchillo</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Palo, hilo resistente</t>
+    </r>
   </si>
   <si>
-    <t>Cinta aislante</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Hilo resistente</t>
+    </r>
   </si>
   <si>
-    <t>Lanza</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Radio</t>
+    </r>
   </si>
   <si>
-    <t>Palo, cuchillo, cinta aislante</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>La necesitas con pilas para investigar</t>
+    </r>
   </si>
   <si>
-    <t>Pilas</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Aguja</t>
+    </r>
   </si>
   <si>
-    <t>Linterna</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>22</t>
+    </r>
   </si>
   <si>
-    <t>Palanca</t>
-  </si>
-  <si>
-    <t>Para entrar en sitios</t>
-  </si>
-  <si>
-    <t>Comida</t>
-  </si>
-  <si>
-    <t>Agua</t>
-  </si>
-  <si>
-    <t>Cuerda</t>
-  </si>
-  <si>
-    <t>Arco</t>
-  </si>
-  <si>
-    <t>Flecha</t>
-  </si>
-  <si>
-    <t>Solo si tienes arco. Se pueden recuperar cuando finaliza el combate</t>
-  </si>
-  <si>
-    <t>Saco de dormir</t>
-  </si>
-  <si>
-    <t>Evita heridas si no duermes en un enclave principal?</t>
-  </si>
-  <si>
-    <t>Pico escalada</t>
-  </si>
-  <si>
-    <t>Palo, hilo resistente</t>
-  </si>
-  <si>
-    <t>Hilo resistente</t>
-  </si>
-  <si>
-    <t>Radio</t>
-  </si>
-  <si>
-    <t>La necesitas con pilas para investigar</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Aguja</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>60</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -34562,7 +34889,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1011"/>
+  <dimension ref="A1:J1011"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="12.625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.50390625" customWidth="1"/>
@@ -34574,30 +34901,36 @@
     <col min="7" max="7" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="22.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>5</v>
+        <v>126</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H1" t="s">
-        <v>128</v>
+        <v>131</v>
+      </c>
+      <c r="I1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J1" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -34605,249 +34938,389 @@
         <v>65</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="1"/>
+        <v>133</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="G2" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="3" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H5" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C6" s="14"/>
+        <v>144</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>134</v>
+      </c>
       <c r="D6" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H6" t="s">
         <v>65</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="1" t="s">
+      <c r="H7" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C9" s="14"/>
+        <v>148</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>134</v>
+      </c>
       <c r="D9" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H9" t="s">
         <v>65</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H12" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C16" s="14"/>
+        <v>158</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>134</v>
+      </c>
       <c r="D16" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1">
-        <v>2</v>
+        <v>142</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H16" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -34855,18 +35328,22 @@
         <v>65</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1">
-        <v>4</v>
+        <v>142</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -34874,16 +35351,22 @@
         <v>65</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1">
-        <v>4</v>
+        <v>164</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -34891,33 +35374,48 @@
         <v>65</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="6"/>
+        <v>166</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>134</v>
+      </c>
       <c r="E20" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H20" t="s">
         <v>65</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -34925,14 +35423,22 @@
         <v>65</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1">
-        <v>4</v>
+        <v>168</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -34940,14 +35446,20 @@
         <v>65</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
+        <v>170</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="G22" s="1" t="s">
         <v>159</v>
       </c>
@@ -34957,40 +35469,65 @@
         <v>65</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1">
-        <v>2</v>
+        <v>171</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="7"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
+      <c r="A24" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="9">
-        <f>COUNTIF(Objetos[Confirmado],"S")</f>
-        <v>22</v>
-      </c>
-      <c r="B25" s="9">
-        <f>COUNTA(Objetos[Nombre])</f>
-        <v>22</v>
-      </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9">
-        <f>SUM(G2:G24)</f>
-        <v>60</v>
+      <c r="A25" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">

--- a/design/docs/components_list.xlsx
+++ b/design/docs/components_list.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="174">
   <si>
     <t>Confirmado</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t>Las prisas son malas consejeras</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
   <si>
     <t>Todos</t>
@@ -709,9 +712,6 @@
       </rPr>
       <t>2</t>
     </r>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <r>
@@ -1475,15 +1475,17 @@
       <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1491,17 +1493,17 @@
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1509,17 +1511,17 @@
         <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1527,17 +1529,17 @@
         <v>6</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>1</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1545,17 +1547,17 @@
         <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1563,17 +1565,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1581,17 +1583,17 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>1</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1599,17 +1601,17 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1617,17 +1619,17 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1">
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1635,17 +1637,17 @@
         <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1">
         <v>1</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1653,17 +1655,17 @@
         <v>6</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1671,17 +1673,17 @@
         <v>6</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1">
         <v>1</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1689,17 +1691,17 @@
         <v>6</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1">
         <v>1</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1707,17 +1709,17 @@
         <v>6</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1725,17 +1727,17 @@
         <v>6</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1">
         <v>1</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1743,17 +1745,17 @@
         <v>6</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="1">
         <v>1</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1761,17 +1763,17 @@
         <v>6</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="1">
         <v>1</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1779,17 +1781,17 @@
         <v>6</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1797,17 +1799,17 @@
         <v>6</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="1">
         <v>1</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7818,10 +7820,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>5</v>
@@ -7832,16 +7834,16 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -13959,10 +13961,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -13971,10 +13973,10 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -13983,7 +13985,7 @@
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -17069,50 +17071,50 @@
   <sheetData>
     <row r="1" ht="38.86" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" ht="38.86" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E2" s="5"/>
     </row>
     <row r="3" ht="38.86" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E3" s="14"/>
     </row>
     <row r="4" ht="38.86" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
@@ -17123,85 +17125,85 @@
     </row>
     <row r="5" ht="38.86" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E5" s="5"/>
     </row>
     <row r="6" ht="38.86" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E6" s="5"/>
     </row>
     <row r="7" ht="38.86" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E7" s="5"/>
     </row>
     <row r="8" ht="38.86" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E8" s="5"/>
     </row>
     <row r="9" ht="38.86" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E9" s="5"/>
     </row>
     <row r="10" ht="38.86" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E10" s="15"/>
       <c r="F10" s="16"/>
@@ -17228,64 +17230,64 @@
     </row>
     <row r="11" ht="38.86" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E11" s="5"/>
     </row>
     <row r="12" ht="38.86" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" ht="38.86" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" ht="38.86" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" ht="38.86" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -23327,37 +23329,37 @@
         <v>4</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J1" s="18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N1" s="8"/>
       <c r="O1" s="8"/>
@@ -23381,16 +23383,16 @@
     </row>
     <row r="2" ht="22.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E2" s="1">
         <v>3</v>
@@ -23403,7 +23405,7 @@
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -23413,16 +23415,16 @@
     </row>
     <row r="3" ht="22.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E3" s="1">
         <v>4</v>
@@ -23434,10 +23436,10 @@
         <v>10</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -23447,16 +23449,16 @@
     </row>
     <row r="4" ht="22.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E4" s="1">
         <v>2</v>
@@ -23469,10 +23471,10 @@
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1">
@@ -23481,16 +23483,16 @@
     </row>
     <row r="5" ht="22.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
@@ -23510,13 +23512,13 @@
         <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -23537,16 +23539,16 @@
     </row>
     <row r="7" ht="22.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -23563,16 +23565,16 @@
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -23582,7 +23584,7 @@
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
       <c r="J8" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="1">
@@ -23591,16 +23593,16 @@
     </row>
     <row r="9" ht="22.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -23612,7 +23614,7 @@
         <v>7</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="1"/>
@@ -23623,16 +23625,16 @@
     </row>
     <row r="10" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -23653,16 +23655,16 @@
     </row>
     <row r="11" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -23683,16 +23685,16 @@
     </row>
     <row r="12" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
@@ -23700,14 +23702,14 @@
         <v>2</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L12" s="1">
         <v>1</v>
@@ -23722,13 +23724,13 @@
         <v>6</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -23744,13 +23746,13 @@
         <v>6</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
@@ -23759,7 +23761,7 @@
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
@@ -23767,7 +23769,7 @@
         <v>2</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -23775,13 +23777,13 @@
         <v>6</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E15" s="1">
         <v>3</v>
@@ -23793,10 +23795,10 @@
         <v>8</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
@@ -23804,7 +23806,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -23812,13 +23814,13 @@
         <v>6</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
@@ -23826,18 +23828,18 @@
         <v>4</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
       <c r="K16" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L16" s="1">
         <v>1</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -23845,13 +23847,13 @@
         <v>6</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
@@ -23860,31 +23862,31 @@
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K17" s="6"/>
       <c r="L17" s="1">
         <v>1</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
@@ -23892,11 +23894,11 @@
         <v>5</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I18" s="6"/>
       <c r="J18" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K18" s="6"/>
       <c r="L18" s="1">
@@ -23912,13 +23914,13 @@
         <v>6</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
@@ -23929,13 +23931,13 @@
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
       <c r="K19" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L19" s="1">
         <v>1</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -23985,7 +23987,7 @@
         <v>5</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
@@ -24006,7 +24008,7 @@
         <v>13</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
@@ -34903,429 +34905,429 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H3" t="s">
         <v>137</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="H3" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="H4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="H14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H16" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="17" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>161</v>
@@ -35334,21 +35336,24 @@
         <v>162</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="18" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+      <c r="H17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>163</v>
@@ -35357,93 +35362,102 @@
         <v>164</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="19" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+      <c r="H18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>165</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
+      </c>
+      <c r="H19" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>166</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>167</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>168</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="22" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+      <c r="H21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>169</v>
@@ -35452,59 +35466,65 @@
         <v>170</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="23" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+      <c r="H22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>171</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
+      </c>
+      <c r="H23" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -35515,16 +35535,16 @@
         <v>172</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>173</v>

--- a/design/docs/components_list.xlsx
+++ b/design/docs/components_list.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="212">
   <si>
     <t>Confirmado</t>
   </si>
@@ -23863,7 +23863,7 @@
       <c r="AH1" s="8"/>
       <c r="AI1" s="8"/>
     </row>
-    <row r="2" ht="22.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" ht="22.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -23899,6 +23899,9 @@
       </c>
       <c r="L2" s="1" t="s">
         <v>135</v>
+      </c>
+      <c r="N2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">

--- a/design/docs/components_list.xlsx
+++ b/design/docs/components_list.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="212">
   <si>
     <t>Confirmado</t>
   </si>
@@ -24138,7 +24138,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="9" ht="22.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" ht="22.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -24174,6 +24174,9 @@
       </c>
       <c r="L9" s="1" t="s">
         <v>135</v>
+      </c>
+      <c r="N9" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">

--- a/design/docs/components_list.xlsx
+++ b/design/docs/components_list.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="213">
   <si>
     <t>Confirmado</t>
   </si>
@@ -656,6 +656,9 @@
       </rPr>
       <t>Paso de montaña</t>
     </r>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <r>
@@ -24062,7 +24065,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="7" ht="22.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" ht="22.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -24098,6 +24101,9 @@
       </c>
       <c r="L7" s="1" t="s">
         <v>142</v>
+      </c>
+      <c r="N7" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -24111,7 +24117,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>135</v>
@@ -24149,7 +24155,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>132</v>
@@ -24158,7 +24164,7 @@
         <v>132</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>136</v>
@@ -24190,7 +24196,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>135</v>
@@ -24217,7 +24223,7 @@
         <v>141</v>
       </c>
       <c r="M10" s="20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -24231,7 +24237,7 @@
         <v>15</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>135</v>
@@ -24258,7 +24264,7 @@
         <v>135</v>
       </c>
       <c r="M11" s="20" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -24272,7 +24278,7 @@
         <v>15</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>135</v>
@@ -24299,7 +24305,7 @@
         <v>142</v>
       </c>
       <c r="M12" s="20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -24313,7 +24319,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>135</v>
@@ -24351,7 +24357,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>135</v>
@@ -24360,7 +24366,7 @@
         <v>135</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>135</v>
@@ -24378,7 +24384,7 @@
         <v>141</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -24392,13 +24398,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>132</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>134</v>
@@ -24419,7 +24425,7 @@
         <v>135</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -24433,7 +24439,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>135</v>
@@ -24460,7 +24466,7 @@
         <v>142</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -24474,7 +24480,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>135</v>
@@ -24501,7 +24507,7 @@
         <v>142</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -24515,7 +24521,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>135</v>
@@ -24542,7 +24548,7 @@
         <v>141</v>
       </c>
       <c r="M18" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -24556,7 +24562,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>135</v>
@@ -24583,7 +24589,7 @@
         <v>142</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -24646,10 +24652,10 @@
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>135</v>
@@ -24704,10 +24710,10 @@
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C24" s="22" t="s">
         <v>144</v>
@@ -35629,28 +35635,28 @@
         <v>119</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -35658,7 +35664,7 @@
         <v>15</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>135</v>
@@ -35673,7 +35679,7 @@
         <v>135</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H2" t="s">
         <v>143</v>
@@ -35684,7 +35690,7 @@
         <v>15</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>135</v>
@@ -35710,7 +35716,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>135</v>
@@ -35736,10 +35742,10 @@
         <v>15</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>135</v>
@@ -35748,7 +35754,7 @@
         <v>136</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>135</v>
@@ -35762,7 +35768,7 @@
         <v>15</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>135</v>
@@ -35788,7 +35794,7 @@
         <v>15</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>135</v>
@@ -35814,7 +35820,7 @@
         <v>15</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>135</v>
@@ -35840,7 +35846,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>135</v>
@@ -35852,7 +35858,7 @@
         <v>136</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>135</v>
@@ -35866,7 +35872,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>135</v>
@@ -35892,7 +35898,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>135</v>
@@ -35918,10 +35924,10 @@
         <v>15</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>136</v>
@@ -35944,7 +35950,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>135</v>
@@ -35970,7 +35976,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>135</v>
@@ -35996,7 +36002,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>135</v>
@@ -36022,7 +36028,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>135</v>
@@ -36048,10 +36054,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>136</v>
@@ -36077,7 +36083,7 @@
         <v>147</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>135</v>
@@ -36100,7 +36106,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>135</v>
@@ -36126,7 +36132,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C20" s="14" t="s">
         <v>135</v>
@@ -36138,7 +36144,7 @@
         <v>136</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>135</v>
@@ -36152,7 +36158,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>135</v>
@@ -36178,10 +36184,10 @@
         <v>15</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>135</v>
@@ -36204,7 +36210,7 @@
         <v>15</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>135</v>
@@ -36247,10 +36253,10 @@
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>135</v>
@@ -36265,7 +36271,7 @@
         <v>135</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">

--- a/design/docs/components_list.xlsx
+++ b/design/docs/components_list.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="212">
   <si>
     <t>Confirmado</t>
   </si>
@@ -656,9 +656,6 @@
       </rPr>
       <t>Paso de montaña</t>
     </r>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <r>
@@ -24024,7 +24021,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="6" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" ht="22.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -24063,6 +24060,9 @@
       </c>
       <c r="M6" s="20" t="s">
         <v>147</v>
+      </c>
+      <c r="N6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -24103,7 +24103,7 @@
         <v>142</v>
       </c>
       <c r="N7" t="s">
-        <v>149</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -24117,7 +24117,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>135</v>
@@ -24155,7 +24155,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>132</v>
@@ -24164,7 +24164,7 @@
         <v>132</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>136</v>
@@ -24196,7 +24196,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>135</v>
@@ -24223,7 +24223,7 @@
         <v>141</v>
       </c>
       <c r="M10" s="20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -24237,7 +24237,7 @@
         <v>15</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>135</v>
@@ -24264,10 +24264,10 @@
         <v>135</v>
       </c>
       <c r="M11" s="20" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="12" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -24278,7 +24278,7 @@
         <v>15</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>135</v>
@@ -24305,7 +24305,10 @@
         <v>142</v>
       </c>
       <c r="M12" s="20" t="s">
-        <v>158</v>
+        <v>157</v>
+      </c>
+      <c r="N12" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -24319,7 +24322,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>135</v>
@@ -24357,7 +24360,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>135</v>
@@ -24366,7 +24369,7 @@
         <v>135</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>135</v>
@@ -24384,7 +24387,7 @@
         <v>141</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -24398,13 +24401,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>132</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>134</v>
@@ -24425,7 +24428,7 @@
         <v>135</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -24439,7 +24442,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>135</v>
@@ -24466,7 +24469,7 @@
         <v>142</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -24480,7 +24483,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>135</v>
@@ -24507,7 +24510,7 @@
         <v>142</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -24521,7 +24524,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>135</v>
@@ -24548,7 +24551,7 @@
         <v>141</v>
       </c>
       <c r="M18" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -24562,7 +24565,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>135</v>
@@ -24589,7 +24592,7 @@
         <v>142</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -24652,10 +24655,10 @@
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>135</v>
@@ -24710,10 +24713,10 @@
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C24" s="22" t="s">
         <v>144</v>
@@ -35635,28 +35638,28 @@
         <v>119</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="G1" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -35664,7 +35667,7 @@
         <v>15</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>135</v>
@@ -35679,7 +35682,7 @@
         <v>135</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H2" t="s">
         <v>143</v>
@@ -35690,7 +35693,7 @@
         <v>15</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>135</v>
@@ -35716,7 +35719,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>135</v>
@@ -35742,10 +35745,10 @@
         <v>15</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>135</v>
@@ -35754,7 +35757,7 @@
         <v>136</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>135</v>
@@ -35768,7 +35771,7 @@
         <v>15</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>135</v>
@@ -35794,7 +35797,7 @@
         <v>15</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>135</v>
@@ -35820,7 +35823,7 @@
         <v>15</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>135</v>
@@ -35846,7 +35849,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>135</v>
@@ -35858,7 +35861,7 @@
         <v>136</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>135</v>
@@ -35872,7 +35875,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>135</v>
@@ -35898,7 +35901,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>135</v>
@@ -35924,10 +35927,10 @@
         <v>15</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>196</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>197</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>136</v>
@@ -35950,7 +35953,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>135</v>
@@ -35976,7 +35979,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>135</v>
@@ -36002,7 +36005,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>135</v>
@@ -36028,7 +36031,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>135</v>
@@ -36054,10 +36057,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>203</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>136</v>
@@ -36083,7 +36086,7 @@
         <v>147</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>135</v>
@@ -36106,7 +36109,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>135</v>
@@ -36132,7 +36135,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C20" s="14" t="s">
         <v>135</v>
@@ -36144,7 +36147,7 @@
         <v>136</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>135</v>
@@ -36158,7 +36161,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>135</v>
@@ -36184,10 +36187,10 @@
         <v>15</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>208</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>209</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>135</v>
@@ -36210,7 +36213,7 @@
         <v>15</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>135</v>
@@ -36253,10 +36256,10 @@
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>135</v>
@@ -36271,7 +36274,7 @@
         <v>135</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">

--- a/design/docs/components_list.xlsx
+++ b/design/docs/components_list.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="212">
   <si>
     <t>Confirmado</t>
   </si>
@@ -658,13 +658,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-      </rPr>
-      <t>Zona boscosa</t>
-    </r>
+    <t>Bosque cerrado</t>
   </si>
   <si>
     <r>
@@ -24106,7 +24100,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="22.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" ht="22.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -24142,6 +24136,9 @@
       </c>
       <c r="L8" s="1" t="s">
         <v>141</v>
+      </c>
+      <c r="N8" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -24311,7 +24308,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" ht="22.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" ht="22.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
@@ -24347,6 +24344,9 @@
       </c>
       <c r="L13" s="6" t="s">
         <v>135</v>
+      </c>
+      <c r="N13" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">

--- a/design/docs/components_list.xlsx
+++ b/design/docs/components_list.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="215">
   <si>
     <t>Confirmado</t>
   </si>
@@ -487,6 +487,9 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+      </rPr>
       <t>Implementado</t>
     </r>
   </si>
@@ -658,7 +661,23 @@
     </r>
   </si>
   <si>
-    <t>Bosque cerrado</t>
+    <r>
+      <t>Zona boscosa</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>Bosque cerrado</t>
+    </r>
   </si>
   <si>
     <r>
@@ -838,6 +857,15 @@
         <i/>
       </rPr>
       <t>Pilas, Radio</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+      </rPr>
+      <t>N</t>
     </r>
   </si>
   <si>
@@ -23777,7 +23805,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AI1009"/>
+  <dimension ref="A1:AI1010"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="12.625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.50390625" customWidth="1"/>
@@ -24100,45 +24128,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="22.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="4" t="s">
+    <row r="8" ht="22.5" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>144</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" t="s">
         <v>149</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="N8" t="s">
-        <v>15</v>
+      <c r="G8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -24146,66 +24147,66 @@
         <v>15</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="E9" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>136</v>
+      <c r="H9" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>135</v>
       </c>
       <c r="J9" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K9" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="L9" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="N9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" ht="22.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>135</v>
+      <c r="E10" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>135</v>
+        <v>153</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>135</v>
@@ -24217,10 +24218,10 @@
         <v>135</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="M10" s="20" t="s">
-        <v>153</v>
+        <v>135</v>
+      </c>
+      <c r="N10" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -24243,7 +24244,7 @@
         <v>135</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>135</v>
@@ -24258,13 +24259,13 @@
         <v>135</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="M11" s="20" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="12" ht="22.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -24284,39 +24285,36 @@
         <v>135</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>135</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="M12" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="N12" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="13" ht="22.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>144</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>158</v>
@@ -24327,29 +24325,32 @@
       <c r="F13" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>135</v>
+      <c r="K13" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="M13" s="20" t="s">
+        <v>159</v>
       </c>
       <c r="N13" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" ht="22.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
@@ -24360,7 +24361,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>135</v>
@@ -24368,14 +24369,14 @@
       <c r="F14" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>160</v>
+      <c r="G14" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>136</v>
+      <c r="I14" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>135</v>
@@ -24383,37 +24384,37 @@
       <c r="K14" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="15" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L14" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="N14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>136</v>
+      <c r="H15" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>136</v>
@@ -24425,10 +24426,13 @@
         <v>135</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="M15" s="4" t="s">
         <v>163</v>
+      </c>
+      <c r="N15" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -24436,7 +24440,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>8</v>
@@ -24444,29 +24448,29 @@
       <c r="D16" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>135</v>
+      <c r="E16" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>162</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="I16" s="6" t="s">
-        <v>135</v>
+      <c r="I16" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>136</v>
+      <c r="K16" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="M16" s="4" t="s">
         <v>165</v>
@@ -24494,17 +24498,17 @@
       <c r="G17" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H17" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I17" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>142</v>
@@ -24515,7 +24519,7 @@
     </row>
     <row r="18" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>144</v>
@@ -24533,13 +24537,13 @@
         <v>135</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="H18" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>136</v>
@@ -24548,15 +24552,15 @@
         <v>135</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="M18" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="M18" s="4" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>144</v>
@@ -24574,54 +24578,66 @@
         <v>135</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="J19" s="6" t="s">
+      <c r="J19" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K19" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="L19" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="M19" s="20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="M19" s="4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>135</v>
+      <c r="M20" s="4" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -24653,73 +24669,67 @@
         <v>135</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="C22" s="10" t="s">
+    <row r="22" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="E22" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="F22" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="G22" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="H22" s="7" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="B23" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="E23" s="7" t="s">
+      <c r="I22" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="J22" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="K22" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="L22" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="I23" s="7" t="s">
+    </row>
+    <row r="23" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="J23" s="7" t="s">
+      <c r="D23" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="K23" s="7" t="s">
+      <c r="E23" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="L23" s="7" t="s">
+      <c r="F23" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="G23" s="9" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>135</v>
@@ -24747,15 +24757,39 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
+      <c r="A25" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
@@ -35580,6 +35614,17 @@
       <c r="J1009" s="7"/>
       <c r="K1009" s="7"/>
       <c r="L1009" s="7"/>
+    </row>
+    <row r="1010" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1010" s="7"/>
+      <c r="E1010" s="7"/>
+      <c r="F1010" s="7"/>
+      <c r="G1010" s="7"/>
+      <c r="H1010" s="7"/>
+      <c r="I1010" s="7"/>
+      <c r="J1010" s="7"/>
+      <c r="K1010" s="7"/>
+      <c r="L1010" s="7"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A22:B24 G22">
@@ -35638,28 +35683,28 @@
         <v>119</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="J1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -35667,7 +35712,7 @@
         <v>15</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>135</v>
@@ -35682,7 +35727,7 @@
         <v>135</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H2" t="s">
         <v>143</v>
@@ -35693,7 +35738,7 @@
         <v>15</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>135</v>
@@ -35719,7 +35764,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>135</v>
@@ -35745,10 +35790,10 @@
         <v>15</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>135</v>
@@ -35757,7 +35802,7 @@
         <v>136</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>135</v>
@@ -35771,7 +35816,7 @@
         <v>15</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>135</v>
@@ -35797,7 +35842,7 @@
         <v>15</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>135</v>
@@ -35823,7 +35868,7 @@
         <v>15</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>135</v>
@@ -35849,7 +35894,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>135</v>
@@ -35861,7 +35906,7 @@
         <v>136</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>135</v>
@@ -35875,7 +35920,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>135</v>
@@ -35901,7 +35946,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>135</v>
@@ -35927,10 +35972,10 @@
         <v>15</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>136</v>
@@ -35953,7 +35998,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>135</v>
@@ -35979,7 +36024,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>135</v>
@@ -36005,7 +36050,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>135</v>
@@ -36031,7 +36076,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>135</v>
@@ -36057,10 +36102,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>136</v>
@@ -36086,7 +36131,7 @@
         <v>147</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>135</v>
@@ -36109,7 +36154,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>135</v>
@@ -36135,7 +36180,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C20" s="14" t="s">
         <v>135</v>
@@ -36147,7 +36192,7 @@
         <v>136</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>135</v>
@@ -36161,7 +36206,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>135</v>
@@ -36187,10 +36232,10 @@
         <v>15</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>135</v>
@@ -36213,7 +36258,7 @@
         <v>15</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>135</v>
@@ -36256,10 +36301,10 @@
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>135</v>
@@ -36274,7 +36319,7 @@
         <v>135</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">

--- a/design/docs/components_list.xlsx
+++ b/design/docs/components_list.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="260">
   <si>
     <t>Confirmado</t>
   </si>
@@ -393,6 +393,9 @@
   </si>
   <si>
     <t>Copias</t>
+  </si>
+  <si>
+    <t>Notas</t>
   </si>
   <si>
     <t>Principal</t>
@@ -777,15 +780,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <rFont val="Calibri"/>
-        <sz val="11"/>
-      </rPr>
-      <t>Puerto pesquero en ruinas</t>
-    </r>
+    <t>Pueblo pesquero en ruinas</t>
   </si>
   <si>
     <r>
@@ -797,6 +792,9 @@
       </rPr>
       <t>-</t>
     </r>
+  </si>
+  <si>
+    <t>Solo debería estar en los bordes del mapa?</t>
   </si>
   <si>
     <r>
@@ -1545,7 +1543,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
@@ -1624,6 +1622,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
@@ -1733,8 +1732,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Enclaves" displayName="Enclaves" ref="B1:M19" headerRowCount="0">
-  <tableColumns count="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Enclaves" displayName="Enclaves" ref="B1:N19" headerRowCount="0">
+  <tableColumns count="13">
     <tableColumn id="3" name="Fijo en mapa"/>
     <tableColumn id="4" name="Nombre"/>
     <tableColumn id="5" name="Asentamiento Max"/>
@@ -1747,6 +1746,7 @@
     <tableColumn id="12" name="Dados de encuentro"/>
     <tableColumn id="13" name="Requisito" dataDxfId="2"/>
     <tableColumn id="1" name="Column1"/>
+    <tableColumn id="2" name="Column2"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1993,7 +1993,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{732BDB18-53A9-46A8-B331-D861D99956A9}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{400C5CB2-2D28-4F0F-BAA4-4B211B9EF1D9}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -8447,7 +8447,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{020D8F9B-7179-477B-96FC-344C05BE8140}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{0EB52F6E-FC11-4DDE-A06A-4EBDDEFB769A}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -14590,7 +14590,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{30CCC1AA-B14D-4CB7-8338-6594AA17487F}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{66FB50AE-6428-4E7A-B904-341D33AEDF92}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17708,7 +17708,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{76F88E49-6169-4AA5-BBB3-30ED7F1710AE}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{D25A4660-3EC6-41A6-92FA-84040DEFB60B}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -23954,7 +23954,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{5D76AE47-39B8-489E-98C6-1C23CDEA7038}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{29273B2D-0EE0-4D67-BA3D-BC0EF4BA4803}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -24013,7 +24013,9 @@
       <c r="M1" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="N1" s="8"/>
+      <c r="N1" s="17" t="s">
+        <v>125</v>
+      </c>
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
@@ -24035,219 +24037,219 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="J3" s="22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L3" s="23"/>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="J4" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L5" s="23"/>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L7" s="23" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E8" s="22">
         <v>1</v>
@@ -24257,569 +24259,572 @@
         <v>1</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H9" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="J9" s="22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F10" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="H10" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J11" s="24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L11" s="23"/>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L12" s="23"/>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F13" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="I13" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J13" s="24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G15" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="H15" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="H15" s="6" t="s">
-        <v>130</v>
-      </c>
       <c r="I15" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L15" s="23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F16" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="I16" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H16" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="J16" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L16" s="23"/>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F17" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="G17" s="6" t="s">
-        <v>130</v>
-      </c>
       <c r="H17" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L17" s="23"/>
+      <c r="M17" s="28" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G18" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H18" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="J18" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L18" s="23"/>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F19" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="H19" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="J19" s="24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K19" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L19" s="23"/>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K20" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="B21" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J21" s="26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="B22" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J22" s="26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="B23" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="B24" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J24" s="26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="B25" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J25" s="26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -34697,7 +34702,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{6D945D59-3F69-40EB-B4CE-3E0D651BC1B9}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{0C257623-63A8-4695-A3D0-71D954C2F418}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -34715,649 +34720,649 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="F1" s="28" t="s">
-        <v>182</v>
+        <v>183</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>184</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="H5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>130</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>130</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H8" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="H9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>130</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H13" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H14" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H15" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>130</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H16" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>130</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H18" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H19" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="H20" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H21" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H22" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H23" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="9" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">

--- a/design/docs/components_list.xlsx
+++ b/design/docs/components_list.xlsx
@@ -1421,7 +1421,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -1453,13 +1453,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -1543,7 +1536,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
@@ -1593,36 +1586,35 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
@@ -1993,7 +1985,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{400C5CB2-2D28-4F0F-BAA4-4B211B9EF1D9}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{22D6024D-22C3-4B8B-8F45-AE8578F9588C}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -8425,10 +8417,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A20" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A20" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8447,7 +8439,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{0EB52F6E-FC11-4DDE-A06A-4EBDDEFB769A}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{16CEB281-6806-416B-993C-15536F463DEA}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -14568,10 +14560,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A20" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A20" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14590,7 +14582,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{66FB50AE-6428-4E7A-B904-341D33AEDF92}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{7E6DA6EF-7498-4668-8E98-260F4357FA56}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17686,10 +17678,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A14" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A14" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17708,7 +17700,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{D25A4660-3EC6-41A6-92FA-84040DEFB60B}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{A151E500-D24E-482F-B193-62D5D41292D6}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -23932,10 +23924,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B10:C14" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B2:C9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B2:C9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B10:C14" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23954,7 +23946,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{29273B2D-0EE0-4D67-BA3D-BC0EF4BA4803}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{BAE19906-857E-4D7C-8496-1B15E0A207DA}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -24586,7 +24578,7 @@
         <v>171</v>
       </c>
       <c r="L17" s="23"/>
-      <c r="M17" s="28" t="s">
+      <c r="M17" s="25" t="s">
         <v>172</v>
       </c>
     </row>
@@ -34684,8 +34676,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
+    <dataValidation allowBlank="1" errorStyle="warning" showErrorMessage="1" showInputMessage="1" sqref="B2"/>
     <dataValidation allowBlank="1" errorStyle="warning" showErrorMessage="1" showInputMessage="1" sqref="B3:B20"/>
-    <dataValidation allowBlank="1" errorStyle="warning" showErrorMessage="1" showInputMessage="1" sqref="B2"/>
   </dataValidations>
   <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -34702,7 +34694,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{0C257623-63A8-4695-A3D0-71D954C2F418}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{BAB7746D-7502-49D0-A536-9EDC8569791A}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -34734,7 +34726,7 @@
       <c r="E1" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="28" t="s">
         <v>184</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -43260,10 +43252,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A23" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A23" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>

--- a/design/docs/components_list.xlsx
+++ b/design/docs/components_list.xlsx
@@ -441,17 +441,6 @@
         <rFont val="Calibri"/>
         <sz val="11"/>
       </rPr>
-      <t>8</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <rFont val="Calibri"/>
-        <sz val="11"/>
-      </rPr>
       <t xml:space="preserve"> </t>
     </r>
   </si>
@@ -489,17 +478,6 @@
         <sz val="11"/>
       </rPr>
       <t>4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <rFont val="Calibri"/>
-        <sz val="11"/>
-      </rPr>
-      <t>10</t>
     </r>
   </si>
   <si>
@@ -625,17 +603,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <rFont val="Calibri"/>
-        <sz val="11"/>
-      </rPr>
-      <t>7</t>
-    </r>
-  </si>
-  <si>
     <t>S</t>
   </si>
   <si>
@@ -740,17 +707,6 @@
         <rFont val="Calibri"/>
         <sz val="11"/>
       </rPr>
-      <t>6</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <rFont val="Calibri"/>
-        <sz val="11"/>
-      </rPr>
       <t>Tarjeta de acceso militar</t>
     </r>
   </si>
@@ -766,6 +722,28 @@
         <sz val="11"/>
       </rPr>
       <t>Búnker subterráneo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <rFont val="Calibri"/>
+        <sz val="11"/>
+      </rPr>
+      <t>6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <rFont val="Calibri"/>
+        <sz val="11"/>
+      </rPr>
+      <t>8</t>
     </r>
   </si>
   <si>
@@ -861,6 +839,12 @@
       </rPr>
       <t>Herramientas mecánicas</t>
     </r>
+  </si>
+  <si>
+    <t>Estación de radio abandonada</t>
+  </si>
+  <si>
+    <t>S</t>
   </si>
   <si>
     <r>
@@ -1985,7 +1969,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{22D6024D-22C3-4B8B-8F45-AE8578F9588C}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{99159FD6-8E07-40E7-A0F3-8982EF2F460B}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -8417,10 +8401,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A20" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A20" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8439,7 +8423,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{16CEB281-6806-416B-993C-15536F463DEA}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{200B2000-E6B3-499C-B954-7FC5C2F8457A}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -14560,10 +14544,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A20" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A20" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14582,7 +14566,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{7E6DA6EF-7498-4668-8E98-260F4357FA56}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{B2368F40-ED6D-46E0-A9A2-D5E917612A73}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17678,10 +17662,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A14" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A14" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17700,7 +17684,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{A151E500-D24E-482F-B193-62D5D41292D6}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{4FAFF22E-72FD-4D04-8C3F-B4AC7DF4BC72}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -23924,10 +23908,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B2:C9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B10:C14" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B10:C14" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B2:C9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23946,7 +23930,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{BAE19906-857E-4D7C-8496-1B15E0A207DA}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{EC8277F0-FD24-4BA3-BCE0-9BCFB13E34A4}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -24040,26 +24024,26 @@
       <c r="D2" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="6">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="L2" s="23" t="s">
         <v>132</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="J2" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="L2" s="23" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
@@ -24067,31 +24051,31 @@
         <v>126</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>136</v>
+      <c r="E3" s="1">
+        <v>5</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L3" s="23"/>
     </row>
@@ -24100,148 +24084,148 @@
         <v>126</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4" s="6">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J4" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="L4" s="23" t="s">
         <v>138</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="J4" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="L4" s="23" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L5" s="23"/>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="K6" t="s">
+        <v>142</v>
+      </c>
+      <c r="L6" s="23" t="s">
         <v>143</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="K6" t="s">
-        <v>144</v>
-      </c>
-      <c r="L6" s="23" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>138</v>
+        <v>130</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L7" s="23" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E8" s="22">
         <v>1</v>
@@ -24251,42 +24235,42 @@
         <v>1</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H9" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>132</v>
-      </c>
       <c r="I9" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J9" s="22" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
@@ -24294,7 +24278,7 @@
         <v>126</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>128</v>
@@ -24302,171 +24286,171 @@
       <c r="D10" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>153</v>
+      <c r="E10" s="1">
+        <v>3</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J11" s="24" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="L11" s="23"/>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K12" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="L12" s="23"/>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="H13" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="J13" s="24" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K13" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
@@ -24474,45 +24458,45 @@
         <v>126</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C15" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E15" s="6">
+        <v>4</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G15" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>132</v>
-      </c>
       <c r="H15" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K15" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="L15" s="23" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>128</v>
@@ -24521,302 +24505,308 @@
         <v>165</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>131</v>
-      </c>
       <c r="I16" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K16" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L16" s="23"/>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C17" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="G17" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="J17" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K17" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L17" s="23"/>
       <c r="M17" s="25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C18" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="H18" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>132</v>
-      </c>
       <c r="I18" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K18" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="L18" s="23"/>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C19" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" s="1">
+        <v>3</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="G19" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H19" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>132</v>
-      </c>
       <c r="I19" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J19" s="24" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K19" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L19" s="23"/>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F20" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="J20" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K20" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C21" s="7">
+        <v>3</v>
+      </c>
+      <c r="D21" s="7">
+        <v>2</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="J21" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="L21" s="27" t="s">
         <v>178</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="B21" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="J21" s="26" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="B22" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J22" s="26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="B23" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="B24" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J24" s="26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="B25" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J25" s="26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -34676,8 +34666,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
+    <dataValidation allowBlank="1" errorStyle="warning" showErrorMessage="1" showInputMessage="1" sqref="B3:B20"/>
     <dataValidation allowBlank="1" errorStyle="warning" showErrorMessage="1" showInputMessage="1" sqref="B2"/>
-    <dataValidation allowBlank="1" errorStyle="warning" showErrorMessage="1" showInputMessage="1" sqref="B3:B20"/>
   </dataValidations>
   <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -34694,7 +34684,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{BAB7746D-7502-49D0-A536-9EDC8569791A}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{B910040C-8F5B-4BE5-BD47-B20EFD011F1D}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -34750,22 +34740,22 @@
         <v>188</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>189</v>
       </c>
       <c r="H2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
@@ -34776,22 +34766,22 @@
         <v>191</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>128</v>
       </c>
       <c r="H3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
@@ -34802,16 +34792,16 @@
         <v>193</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>128</v>
@@ -34831,16 +34821,16 @@
         <v>197</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>198</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H5" t="s">
         <v>199</v>
@@ -34854,19 +34844,19 @@
         <v>201</v>
       </c>
       <c r="C6" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="E6" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H6" t="s">
         <v>202</v>
@@ -34880,16 +34870,16 @@
         <v>204</v>
       </c>
       <c r="C7" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="E7" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>128</v>
@@ -34906,19 +34896,19 @@
         <v>207</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H8" t="s">
         <v>208</v>
@@ -34932,19 +34922,19 @@
         <v>210</v>
       </c>
       <c r="C9" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>211</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H9" t="s">
         <v>212</v>
@@ -34958,19 +34948,19 @@
         <v>214</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H10" t="s">
         <v>215</v>
@@ -34984,16 +34974,16 @@
         <v>217</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>128</v>
@@ -35013,13 +35003,13 @@
         <v>221</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>128</v>
@@ -35036,16 +35026,16 @@
         <v>224</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>129</v>
@@ -35062,16 +35052,16 @@
         <v>227</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>129</v>
@@ -35088,16 +35078,16 @@
         <v>230</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>128</v>
@@ -35114,19 +35104,19 @@
         <v>233</v>
       </c>
       <c r="C16" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="E16" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H16" t="s">
         <v>234</v>
@@ -35143,16 +35133,16 @@
         <v>237</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H17" t="s">
         <v>238</v>
@@ -35163,22 +35153,22 @@
         <v>239</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>240</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H18" t="s">
         <v>241</v>
@@ -35192,19 +35182,19 @@
         <v>243</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H19" t="s">
         <v>244</v>
@@ -35215,22 +35205,22 @@
         <v>245</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C20" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>246</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H20" t="s">
         <v>247</v>
@@ -35244,19 +35234,19 @@
         <v>249</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H21" t="s">
         <v>250</v>
@@ -35273,16 +35263,16 @@
         <v>253</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H22" t="s">
         <v>254</v>
@@ -35296,19 +35286,19 @@
         <v>256</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H23" t="s">
         <v>257</v>
@@ -35316,22 +35306,22 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -35342,16 +35332,16 @@
         <v>258</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>259</v>
@@ -43252,10 +43242,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A23" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A23" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>

--- a/design/docs/components_list.xlsx
+++ b/design/docs/components_list.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
   <si>
     <t>Confirmado</t>
   </si>
@@ -845,6 +845,9 @@
   </si>
   <si>
     <t>S</t>
+  </si>
+  <si>
+    <t>Praderas</t>
   </si>
   <si>
     <r>
@@ -1969,7 +1972,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{99159FD6-8E07-40E7-A0F3-8982EF2F460B}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{E4DE96A6-A22B-4496-803D-557EFD0ACDC6}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -8401,10 +8404,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A20" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A20" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8423,7 +8426,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{200B2000-E6B3-499C-B954-7FC5C2F8457A}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{7AE79A31-B1B9-4FF9-B772-9074E67FC253}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -14544,10 +14547,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A20" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A20" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14566,7 +14569,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{B2368F40-ED6D-46E0-A9A2-D5E917612A73}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{C0C98B2F-A7F5-465E-8E88-FA7B2387AA5A}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17662,10 +17665,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A14" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A14" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17684,7 +17687,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{4FAFF22E-72FD-4D04-8C3F-B4AC7DF4BC72}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{CD341524-7A3F-4EE1-85A8-78BDF4F2F6F6}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -23908,10 +23911,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B10:C14" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B2:C9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B2:C9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B10:C14" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23930,7 +23933,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{EC8277F0-FD24-4BA3-BCE0-9BCFB13E34A4}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{3FBA2817-99AC-4572-94B0-CA8D389F7656}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -24154,11 +24157,11 @@
       <c r="B6" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>130</v>
+      <c r="C6" s="6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>136</v>
@@ -24701,16 +24704,19 @@
       <c r="I21" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="J21" s="26" t="s">
-        <v>130</v>
+      <c r="J21" s="26">
+        <v>0</v>
       </c>
       <c r="L21" s="27" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="21" t="s">
+        <v>139</v>
+      </c>
       <c r="B22" s="7" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>130</v>
@@ -24718,8 +24724,8 @@
       <c r="D22" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>130</v>
+      <c r="E22" s="7">
+        <v>1</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>130</v>
@@ -24727,14 +24733,14 @@
       <c r="G22" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="H22" s="7" t="s">
-        <v>130</v>
+      <c r="H22" s="7">
+        <v>1</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="J22" s="26" t="s">
-        <v>130</v>
+      <c r="J22" s="26">
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -34666,8 +34672,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
+    <dataValidation allowBlank="1" errorStyle="warning" showErrorMessage="1" showInputMessage="1" sqref="B2"/>
     <dataValidation allowBlank="1" errorStyle="warning" showErrorMessage="1" showInputMessage="1" sqref="B3:B20"/>
-    <dataValidation allowBlank="1" errorStyle="warning" showErrorMessage="1" showInputMessage="1" sqref="B2"/>
   </dataValidations>
   <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -34684,7 +34690,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{B910040C-8F5B-4BE5-BD47-B20EFD011F1D}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{A289B565-E443-4597-ADE8-835CB46A1984}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -34702,42 +34708,42 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>130</v>
@@ -34752,7 +34758,7 @@
         <v>130</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H2" t="s">
         <v>138</v>
@@ -34760,10 +34766,10 @@
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>130</v>
@@ -34786,10 +34792,10 @@
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>130</v>
@@ -34807,18 +34813,18 @@
         <v>128</v>
       </c>
       <c r="H4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>130</v>
@@ -34827,21 +34833,21 @@
         <v>131</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>130</v>
       </c>
       <c r="H5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>130</v>
@@ -34859,15 +34865,15 @@
         <v>134</v>
       </c>
       <c r="H6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>130</v>
@@ -34885,15 +34891,15 @@
         <v>128</v>
       </c>
       <c r="H7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>130</v>
@@ -34911,15 +34917,15 @@
         <v>134</v>
       </c>
       <c r="H8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>130</v>
@@ -34931,21 +34937,21 @@
         <v>131</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>130</v>
       </c>
       <c r="H9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>130</v>
@@ -34963,15 +34969,15 @@
         <v>134</v>
       </c>
       <c r="H10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>130</v>
@@ -34989,18 +34995,18 @@
         <v>128</v>
       </c>
       <c r="H11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>131</v>
@@ -35015,15 +35021,15 @@
         <v>128</v>
       </c>
       <c r="H12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>130</v>
@@ -35041,15 +35047,15 @@
         <v>129</v>
       </c>
       <c r="H13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>130</v>
@@ -35067,15 +35073,15 @@
         <v>129</v>
       </c>
       <c r="H14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>130</v>
@@ -35093,15 +35099,15 @@
         <v>128</v>
       </c>
       <c r="H15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>130</v>
@@ -35119,18 +35125,18 @@
         <v>136</v>
       </c>
       <c r="H16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>131</v>
@@ -35145,18 +35151,18 @@
         <v>134</v>
       </c>
       <c r="H17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>142</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>130</v>
@@ -35171,15 +35177,15 @@
         <v>134</v>
       </c>
       <c r="H18" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>130</v>
@@ -35197,12 +35203,12 @@
         <v>136</v>
       </c>
       <c r="H19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>157</v>
@@ -35217,21 +35223,21 @@
         <v>131</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>130</v>
       </c>
       <c r="H20" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>130</v>
@@ -35249,18 +35255,18 @@
         <v>134</v>
       </c>
       <c r="H21" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>130</v>
@@ -35275,15 +35281,15 @@
         <v>136</v>
       </c>
       <c r="H22" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>130</v>
@@ -35301,7 +35307,7 @@
         <v>136</v>
       </c>
       <c r="H23" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -35326,10 +35332,10 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>130</v>
@@ -35344,7 +35350,7 @@
         <v>130</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -43242,10 +43248,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A23" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A23" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>

--- a/design/docs/components_list.xlsx
+++ b/design/docs/components_list.xlsx
@@ -732,30 +732,11 @@
         <rFont val="Calibri"/>
         <sz val="11"/>
       </rPr>
-      <t>6</t>
+      <t>Código de seguridad o Palanca</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <rFont val="Calibri"/>
-        <sz val="11"/>
-      </rPr>
-      <t>8</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <rFont val="Calibri"/>
-        <sz val="11"/>
-      </rPr>
-      <t>Código de seguridad o Palanca</t>
-    </r>
+    <t>S</t>
   </si>
   <si>
     <t>Pueblo pesquero en ruinas</t>
@@ -848,6 +829,9 @@
   </si>
   <si>
     <t>Praderas</t>
+  </si>
+  <si>
+    <t>S</t>
   </si>
   <si>
     <r>
@@ -1972,7 +1956,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{E4DE96A6-A22B-4496-803D-557EFD0ACDC6}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{1EEE40B6-E774-434A-A019-13D900DA62DE}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -8404,10 +8388,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A20" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A20" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8426,7 +8410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{7AE79A31-B1B9-4FF9-B772-9074E67FC253}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{079E4B70-7386-473D-A234-FE791C2827E3}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -14547,10 +14531,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A20" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A20" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14569,7 +14553,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{C0C98B2F-A7F5-465E-8E88-FA7B2387AA5A}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{54B06525-DD08-40D5-BF68-DE85D534E951}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17665,10 +17649,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A14" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A14" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17687,7 +17671,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{CD341524-7A3F-4EE1-85A8-78BDF4F2F6F6}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{BF814814-7D45-4185-BF90-42E4386B52A4}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -23911,10 +23895,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B2:C9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B10:C14" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B10:C14" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B2:C9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23933,7 +23917,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{3FBA2817-99AC-4572-94B0-CA8D389F7656}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{5D3052C6-C0EE-411D-B856-4C93C0CB4EA5}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -24504,18 +24488,14 @@
       <c r="C16" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>131</v>
-      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>3</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="6"/>
       <c r="H16" s="6" t="s">
         <v>130</v>
       </c>
@@ -24526,16 +24506,18 @@
         <v>130</v>
       </c>
       <c r="K16" t="s">
-        <v>167</v>
-      </c>
-      <c r="L16" s="23"/>
+        <v>165</v>
+      </c>
+      <c r="L16" s="23" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="21" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>130</v>
@@ -24562,11 +24544,11 @@
         <v>137</v>
       </c>
       <c r="K17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L17" s="23"/>
       <c r="M17" s="25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
@@ -24574,7 +24556,7 @@
         <v>139</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>130</v>
@@ -24601,7 +24583,7 @@
         <v>137</v>
       </c>
       <c r="K18" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L18" s="23"/>
     </row>
@@ -24610,7 +24592,7 @@
         <v>139</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>130</v>
@@ -24637,7 +24619,7 @@
         <v>136</v>
       </c>
       <c r="K19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L19" s="23"/>
     </row>
@@ -24646,7 +24628,7 @@
         <v>139</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>130</v>
@@ -24673,7 +24655,7 @@
         <v>137</v>
       </c>
       <c r="K20" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -24681,7 +24663,7 @@
         <v>126</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C21" s="7">
         <v>3</v>
@@ -24708,7 +24690,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="27" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -24716,7 +24698,7 @@
         <v>139</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>130</v>
@@ -24742,8 +24724,12 @@
       <c r="J22" s="26">
         <v>1</v>
       </c>
+      <c r="L22" s="27" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="21"/>
       <c r="B23" s="11" t="s">
         <v>130</v>
       </c>
@@ -34672,8 +34658,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
+    <dataValidation allowBlank="1" errorStyle="warning" showErrorMessage="1" showInputMessage="1" sqref="B3:B20"/>
     <dataValidation allowBlank="1" errorStyle="warning" showErrorMessage="1" showInputMessage="1" sqref="B2"/>
-    <dataValidation allowBlank="1" errorStyle="warning" showErrorMessage="1" showInputMessage="1" sqref="B3:B20"/>
   </dataValidations>
   <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -34690,7 +34676,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{A289B565-E443-4597-ADE8-835CB46A1984}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{D5EB512E-8F61-42F8-9C5B-41C3D6FB0831}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -43248,10 +43234,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A23" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A23" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>

--- a/design/docs/components_list.xlsx
+++ b/design/docs/components_list.xlsx
@@ -1956,7 +1956,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{1EEE40B6-E774-434A-A019-13D900DA62DE}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{90D03273-EDDA-4089-BF9C-21CEE2DC2348}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -8410,7 +8410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{079E4B70-7386-473D-A234-FE791C2827E3}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{962D6972-55B2-45BA-AE55-B6E553C20505}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -14553,7 +14553,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{54B06525-DD08-40D5-BF68-DE85D534E951}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{72ACCF50-354F-450D-8411-93B2056D063B}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17671,7 +17671,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{BF814814-7D45-4185-BF90-42E4386B52A4}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{4BFD8661-0999-4EC5-B237-553773ED9F84}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -23917,7 +23917,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{5D3052C6-C0EE-411D-B856-4C93C0CB4EA5}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{95903C6D-D209-4EFF-BA4D-32D731FC2D71}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -34676,7 +34676,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{D5EB512E-8F61-42F8-9C5B-41C3D6FB0831}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{189EE60D-CDD5-4027-A594-3F827C11F0A4}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>

--- a/design/docs/components_list.xlsx
+++ b/design/docs/components_list.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="262">
   <si>
     <t>Confirmado</t>
   </si>
@@ -811,15 +811,10 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <rFont val="Calibri"/>
-        <sz val="11"/>
-      </rPr>
-      <t>Herramientas mecánicas</t>
-    </r>
+    <t>Palanca</t>
+  </si>
+  <si>
+    <t>S</t>
   </si>
   <si>
     <t>Estación de radio abandonada</t>
@@ -1507,7 +1502,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
@@ -1580,11 +1575,12 @@
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
@@ -1956,7 +1952,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{90D03273-EDDA-4089-BF9C-21CEE2DC2348}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{71B2A03A-AB55-47C1-9034-25DE3FF90B1F}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -8410,7 +8406,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{962D6972-55B2-45BA-AE55-B6E553C20505}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{CD2001DA-4421-486D-BB02-CAC9CD23F138}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -14553,7 +14549,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{72ACCF50-354F-450D-8411-93B2056D063B}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{6416DBC5-9C36-4E09-9DB7-A464F00B8902}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17671,7 +17667,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{4BFD8661-0999-4EC5-B237-553773ED9F84}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{31A5F4EC-A00E-4623-8BBC-711CE4CBD8A8}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -23917,7 +23913,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{95903C6D-D209-4EFF-BA4D-32D731FC2D71}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{F5B15934-2F2D-4DC4-B2EE-756B22248583}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -23927,12 +23923,12 @@
     <col min="2" max="2" width="24.50390625" customWidth="1"/>
     <col min="3" max="3" width="18.50390625" customWidth="1"/>
     <col min="4" max="4" width="12.25390625" customWidth="1"/>
-    <col min="5" max="5" style="26" width="16.50390625" customWidth="1"/>
+    <col min="5" max="5" style="28" width="16.50390625" customWidth="1"/>
     <col min="6" max="6" width="11.00390625" customWidth="1"/>
     <col min="7" max="7" width="9.25390625" customWidth="1"/>
     <col min="8" max="8" width="10.125" customWidth="1"/>
-    <col min="9" max="9" style="26" width="20.375" customWidth="1"/>
-    <col min="10" max="10" style="26" width="11.125" customWidth="1"/>
+    <col min="9" max="9" style="28" width="20.375" customWidth="1"/>
+    <col min="10" max="10" style="28" width="11.125" customWidth="1"/>
     <col min="12" max="12" style="27" width="14.00390625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -24630,11 +24626,11 @@
       <c r="B20" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>130</v>
+      <c r="C20" s="6">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>128</v>
@@ -24654,8 +24650,11 @@
       <c r="J20" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" s="26" t="s">
         <v>175</v>
+      </c>
+      <c r="L20" s="27" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -24663,7 +24662,7 @@
         <v>126</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C21" s="7">
         <v>3</v>
@@ -24686,11 +24685,11 @@
       <c r="I21" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="J21" s="26">
+      <c r="J21" s="28">
         <v>0</v>
       </c>
       <c r="L21" s="27" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -24698,7 +24697,7 @@
         <v>139</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>130</v>
@@ -24721,11 +24720,11 @@
       <c r="I22" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="J22" s="26">
+      <c r="J22" s="28">
         <v>1</v>
       </c>
       <c r="L22" s="27" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -24739,7 +24738,7 @@
       <c r="D23" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="E23" s="28" t="s">
         <v>130</v>
       </c>
     </row>
@@ -24768,7 +24767,7 @@
       <c r="I24" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="J24" s="26" t="s">
+      <c r="J24" s="28" t="s">
         <v>130</v>
       </c>
     </row>
@@ -24797,7 +24796,7 @@
       <c r="I25" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="J25" s="26" t="s">
+      <c r="J25" s="28" t="s">
         <v>130</v>
       </c>
     </row>
@@ -34676,7 +34675,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{189EE60D-CDD5-4027-A594-3F827C11F0A4}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{C090786B-617E-4897-9C2B-4AE1D0B26EC3}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -34694,42 +34693,42 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F1" s="28" t="s">
         <v>185</v>
       </c>
+      <c r="F1" s="29" t="s">
+        <v>186</v>
+      </c>
       <c r="G1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>130</v>
@@ -34744,7 +34743,7 @@
         <v>130</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H2" t="s">
         <v>138</v>
@@ -34752,10 +34751,10 @@
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>130</v>
@@ -34778,10 +34777,10 @@
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>130</v>
@@ -34799,18 +34798,18 @@
         <v>128</v>
       </c>
       <c r="H4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>130</v>
@@ -34819,21 +34818,21 @@
         <v>131</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>130</v>
       </c>
       <c r="H5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>130</v>
@@ -34851,15 +34850,15 @@
         <v>134</v>
       </c>
       <c r="H6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>130</v>
@@ -34877,15 +34876,15 @@
         <v>128</v>
       </c>
       <c r="H7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>130</v>
@@ -34903,15 +34902,15 @@
         <v>134</v>
       </c>
       <c r="H8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>130</v>
@@ -34923,21 +34922,21 @@
         <v>131</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>130</v>
       </c>
       <c r="H9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>130</v>
@@ -34955,15 +34954,15 @@
         <v>134</v>
       </c>
       <c r="H10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>130</v>
@@ -34981,18 +34980,18 @@
         <v>128</v>
       </c>
       <c r="H11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>131</v>
@@ -35007,15 +35006,15 @@
         <v>128</v>
       </c>
       <c r="H12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>130</v>
@@ -35033,15 +35032,15 @@
         <v>129</v>
       </c>
       <c r="H13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>130</v>
@@ -35059,15 +35058,15 @@
         <v>129</v>
       </c>
       <c r="H14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>130</v>
@@ -35085,15 +35084,15 @@
         <v>128</v>
       </c>
       <c r="H15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>130</v>
@@ -35111,18 +35110,18 @@
         <v>136</v>
       </c>
       <c r="H16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>131</v>
@@ -35137,18 +35136,18 @@
         <v>134</v>
       </c>
       <c r="H17" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>142</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>130</v>
@@ -35163,15 +35162,15 @@
         <v>134</v>
       </c>
       <c r="H18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>130</v>
@@ -35189,12 +35188,12 @@
         <v>136</v>
       </c>
       <c r="H19" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>157</v>
@@ -35209,21 +35208,21 @@
         <v>131</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>130</v>
       </c>
       <c r="H20" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>130</v>
@@ -35241,18 +35240,18 @@
         <v>134</v>
       </c>
       <c r="H21" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>130</v>
@@ -35267,15 +35266,15 @@
         <v>136</v>
       </c>
       <c r="H22" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>130</v>
@@ -35293,7 +35292,7 @@
         <v>136</v>
       </c>
       <c r="H23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -35318,10 +35317,10 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>130</v>
@@ -35336,7 +35335,7 @@
         <v>130</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">

--- a/design/docs/components_list.xlsx
+++ b/design/docs/components_list.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
   <si>
     <t>Confirmado</t>
   </si>
@@ -725,15 +725,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <rFont val="Calibri"/>
-        <sz val="11"/>
-      </rPr>
-      <t>Código de seguridad o Palanca</t>
-    </r>
+    <t>Palanca</t>
   </si>
   <si>
     <t>S</t>
@@ -809,9 +801,6 @@
       </rPr>
       <t>Presa hidroeléctrica</t>
     </r>
-  </si>
-  <si>
-    <t>Palanca</t>
   </si>
   <si>
     <t>S</t>
@@ -1502,7 +1491,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
@@ -1582,6 +1571,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
@@ -1952,7 +1942,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{71B2A03A-AB55-47C1-9034-25DE3FF90B1F}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{56CC9A01-FD19-4280-A55F-7A1CE4130B4E}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -8406,7 +8396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{CD2001DA-4421-486D-BB02-CAC9CD23F138}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{635BDDB3-964C-400B-A79A-1559B8F49E9E}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -14549,7 +14539,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{6416DBC5-9C36-4E09-9DB7-A464F00B8902}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{D81CC0BA-C7D2-46B1-A397-DBA9630E74D8}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17667,7 +17657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{31A5F4EC-A00E-4623-8BBC-711CE4CBD8A8}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{40A42BCE-7DCC-445A-842F-8A098DA19A21}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -23913,7 +23903,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{F5B15934-2F2D-4DC4-B2EE-756B22248583}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{B36E38EB-AD19-48F9-B760-B9278EA4517F}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -24501,7 +24491,7 @@
       <c r="J16" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" s="29" t="s">
         <v>165</v>
       </c>
       <c r="L16" s="23" t="s">
@@ -24651,10 +24641,10 @@
         <v>137</v>
       </c>
       <c r="K20" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="L20" s="27" t="s">
         <v>175</v>
-      </c>
-      <c r="L20" s="27" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -24662,7 +24652,7 @@
         <v>126</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C21" s="7">
         <v>3</v>
@@ -24689,7 +24679,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="27" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -24697,7 +24687,7 @@
         <v>139</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>130</v>
@@ -24724,7 +24714,7 @@
         <v>1</v>
       </c>
       <c r="L22" s="27" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -34675,7 +34665,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{C090786B-617E-4897-9C2B-4AE1D0B26EC3}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{E910007B-42B7-4F74-BEEC-80A12EC32458}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -34693,42 +34683,42 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="G1" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>187</v>
       </c>
       <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>190</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>130</v>
@@ -34743,7 +34733,7 @@
         <v>130</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H2" t="s">
         <v>138</v>
@@ -34751,10 +34741,10 @@
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>192</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>193</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>130</v>
@@ -34777,10 +34767,10 @@
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>195</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>130</v>
@@ -34798,18 +34788,18 @@
         <v>128</v>
       </c>
       <c r="H4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>198</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>199</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>130</v>
@@ -34818,21 +34808,21 @@
         <v>131</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>130</v>
       </c>
       <c r="H5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>130</v>
@@ -34850,15 +34840,15 @@
         <v>134</v>
       </c>
       <c r="H6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>205</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>206</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>130</v>
@@ -34876,15 +34866,15 @@
         <v>128</v>
       </c>
       <c r="H7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>208</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>209</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>130</v>
@@ -34902,15 +34892,15 @@
         <v>134</v>
       </c>
       <c r="H8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>130</v>
@@ -34922,21 +34912,21 @@
         <v>131</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>130</v>
       </c>
       <c r="H9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>216</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>130</v>
@@ -34954,15 +34944,15 @@
         <v>134</v>
       </c>
       <c r="H10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>219</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>130</v>
@@ -34980,18 +34970,18 @@
         <v>128</v>
       </c>
       <c r="H11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>222</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>223</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>131</v>
@@ -35006,15 +34996,15 @@
         <v>128</v>
       </c>
       <c r="H12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>225</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>226</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>130</v>
@@ -35032,15 +35022,15 @@
         <v>129</v>
       </c>
       <c r="H13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>228</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>229</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>130</v>
@@ -35058,15 +35048,15 @@
         <v>129</v>
       </c>
       <c r="H14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>232</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>130</v>
@@ -35084,15 +35074,15 @@
         <v>128</v>
       </c>
       <c r="H15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>234</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>235</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>130</v>
@@ -35110,18 +35100,18 @@
         <v>136</v>
       </c>
       <c r="H16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>238</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>239</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>131</v>
@@ -35136,18 +35126,18 @@
         <v>134</v>
       </c>
       <c r="H17" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>142</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>130</v>
@@ -35162,15 +35152,15 @@
         <v>134</v>
       </c>
       <c r="H18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>244</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>245</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>130</v>
@@ -35188,12 +35178,12 @@
         <v>136</v>
       </c>
       <c r="H19" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>157</v>
@@ -35208,21 +35198,21 @@
         <v>131</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>130</v>
       </c>
       <c r="H20" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>251</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>130</v>
@@ -35240,18 +35230,18 @@
         <v>134</v>
       </c>
       <c r="H21" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>254</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>255</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>130</v>
@@ -35266,15 +35256,15 @@
         <v>136</v>
       </c>
       <c r="H22" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>258</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>130</v>
@@ -35292,7 +35282,7 @@
         <v>136</v>
       </c>
       <c r="H23" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -35317,10 +35307,10 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>130</v>
@@ -35335,7 +35325,7 @@
         <v>130</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">

--- a/design/docs/components_list.xlsx
+++ b/design/docs/components_list.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="263">
   <si>
     <t>Confirmado</t>
   </si>
@@ -430,17 +430,6 @@
         <rFont val="Calibri"/>
         <sz val="11"/>
       </rPr>
-      <t>5</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <rFont val="Calibri"/>
-        <sz val="11"/>
-      </rPr>
       <t xml:space="preserve"> </t>
     </r>
   </si>
@@ -470,15 +459,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <rFont val="Calibri"/>
-        <sz val="11"/>
-      </rPr>
-      <t>4</t>
-    </r>
+    <t>S</t>
   </si>
   <si>
     <r>
@@ -500,6 +481,17 @@
         <sz val="11"/>
       </rPr>
       <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <rFont val="Calibri"/>
+        <sz val="11"/>
+      </rPr>
+      <t>4</t>
     </r>
   </si>
   <si>
@@ -743,6 +735,9 @@
       </rPr>
       <t>-</t>
     </r>
+  </si>
+  <si>
+    <t>S</t>
   </si>
   <si>
     <t>Solo debería estar en los bordes del mapa?</t>
@@ -1152,6 +1147,17 @@
         <sz val="11"/>
       </rPr>
       <t>Comida</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <rFont val="Calibri"/>
+        <sz val="11"/>
+      </rPr>
+      <t>5</t>
     </r>
   </si>
   <si>
@@ -1942,7 +1948,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{56CC9A01-FD19-4280-A55F-7A1CE4130B4E}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{A0D90145-DA4A-4D35-A405-685EA153C2F5}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -8396,7 +8402,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{635BDDB3-964C-400B-A79A-1559B8F49E9E}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{FC9D7EA7-B42A-4239-AF62-3BD898FC98AA}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -14539,7 +14545,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{D81CC0BA-C7D2-46B1-A397-DBA9630E74D8}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{97DA6747-FF73-44D8-A08E-782E3ADFC60B}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17657,7 +17663,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{40A42BCE-7DCC-445A-842F-8A098DA19A21}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{09EB0775-0695-466B-881F-ABE37C69475E}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -23903,7 +23909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{B36E38EB-AD19-48F9-B760-B9278EA4517F}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{D049FEC6-3D25-4B64-99FE-3FFD7AA32BEA}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -23994,29 +24000,29 @@
       <c r="C2" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="1">
+        <v>3</v>
+      </c>
+      <c r="E2" s="6">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E2" s="6">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="L2" s="23" t="s">
         <v>131</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="J2" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="L2" s="23" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
@@ -24024,61 +24030,61 @@
         <v>126</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
+      </c>
+      <c r="C3" s="1">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1">
+        <v>3</v>
       </c>
       <c r="E3" s="1">
         <v>5</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>131</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="J3" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="L3" s="23"/>
+        <v>129</v>
+      </c>
+      <c r="J3" s="22">
+        <v>1</v>
+      </c>
+      <c r="L3" s="23" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="21" t="s">
         <v>126</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="E4" s="6">
         <v>3</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="H4" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J4" s="22" t="s">
         <v>137</v>
@@ -24095,25 +24101,25 @@
         <v>140</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J5" s="22" t="s">
         <v>137</v>
@@ -24134,22 +24140,22 @@
         <v>2</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K6" t="s">
         <v>142</v>
@@ -24166,25 +24172,25 @@
         <v>144</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E7" s="6">
         <v>1</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J7" s="22" t="s">
         <v>137</v>
@@ -24219,28 +24225,28 @@
         <v>148</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E9" s="6">
         <v>1</v>
       </c>
       <c r="F9" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H9" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>131</v>
-      </c>
       <c r="I9" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J9" s="22" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L9" s="23" t="s">
         <v>149</v>
@@ -24263,19 +24269,19 @@
         <v>3</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L10" s="23" t="s">
         <v>151</v>
@@ -24289,28 +24295,28 @@
         <v>152</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J11" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K11" t="s">
         <v>153</v>
@@ -24325,28 +24331,28 @@
         <v>154</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>137</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K12" t="s">
         <v>155</v>
@@ -24361,25 +24367,25 @@
         <v>156</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="H13" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="J13" s="24" t="s">
         <v>137</v>
@@ -24399,28 +24405,28 @@
         <v>159</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L14" s="23" t="s">
         <v>160</v>
@@ -24434,28 +24440,28 @@
         <v>161</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E15" s="6">
         <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G15" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="G15" s="6" t="s">
-        <v>131</v>
-      </c>
       <c r="H15" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K15" t="s">
         <v>162</v>
@@ -24483,13 +24489,13 @@
       <c r="F16" s="1"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K16" s="29" t="s">
         <v>165</v>
@@ -24506,25 +24512,25 @@
         <v>167</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G17" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>137</v>
@@ -24532,9 +24538,11 @@
       <c r="K17" t="s">
         <v>168</v>
       </c>
-      <c r="L17" s="23"/>
+      <c r="L17" s="23" t="s">
+        <v>169</v>
+      </c>
       <c r="M17" s="25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
@@ -24542,34 +24550,34 @@
         <v>139</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C18" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="H18" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>131</v>
-      </c>
       <c r="I18" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>137</v>
       </c>
       <c r="K18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L18" s="23"/>
     </row>
@@ -24578,34 +24586,34 @@
         <v>139</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H19" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="H19" s="6" t="s">
-        <v>131</v>
-      </c>
       <c r="I19" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J19" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L19" s="23"/>
     </row>
@@ -24614,7 +24622,7 @@
         <v>139</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C20" s="6">
         <v>1</v>
@@ -24626,16 +24634,16 @@
         <v>128</v>
       </c>
       <c r="F20" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>137</v>
@@ -24644,7 +24652,7 @@
         <v>165</v>
       </c>
       <c r="L20" s="27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -24652,7 +24660,7 @@
         <v>126</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C21" s="7">
         <v>3</v>
@@ -24664,22 +24672,22 @@
         <v>1</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J21" s="28">
         <v>0</v>
       </c>
       <c r="L21" s="27" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -24687,107 +24695,107 @@
         <v>139</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E22" s="7">
         <v>1</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H22" s="7">
         <v>1</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J22" s="28">
         <v>1</v>
       </c>
       <c r="L22" s="27" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="21"/>
       <c r="B23" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="B24" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J24" s="28" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="B25" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J25" s="28" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -34665,7 +34673,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{E910007B-42B7-4F74-BEEC-80A12EC32458}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{5C340BD2-F148-4328-A95B-C7A62EF7266F}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -34683,57 +34691,57 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H2" t="s">
         <v>138</v>
@@ -34741,22 +34749,22 @@
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>128</v>
@@ -34767,565 +34775,565 @@
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>128</v>
       </c>
       <c r="H4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="F5" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C6" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="E6" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C7" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="E7" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>128</v>
       </c>
       <c r="H7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C9" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>128</v>
       </c>
       <c r="H11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>128</v>
       </c>
       <c r="H12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>129</v>
+        <v>227</v>
       </c>
       <c r="H13" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="H14" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>128</v>
       </c>
       <c r="H15" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C16" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="E16" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H16" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H17" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>142</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H18" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H19" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>157</v>
       </c>
       <c r="C20" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="F20" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H20" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H21" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H22" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H23" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">

--- a/design/docs/components_list.xlsx
+++ b/design/docs/components_list.xlsx
@@ -1497,7 +1497,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
@@ -1570,14 +1570,12 @@
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
@@ -1948,7 +1946,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{A0D90145-DA4A-4D35-A405-685EA153C2F5}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{F7653421-B0DF-475D-B084-18DABDA2BA97}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -8380,10 +8378,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A20" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A20" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8402,7 +8400,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{FC9D7EA7-B42A-4239-AF62-3BD898FC98AA}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{0F4D663D-875B-47DF-BCE9-DF4E223F0267}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -14523,10 +14521,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A20" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A20" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14545,7 +14543,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{97DA6747-FF73-44D8-A08E-782E3ADFC60B}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{204E92F7-F602-42C2-B104-7AD30D322341}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17641,10 +17639,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A14" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A14" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17663,7 +17661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{09EB0775-0695-466B-881F-ABE37C69475E}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{8B849210-5482-434D-9B8B-D24E00F38F5B}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -23887,10 +23885,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B10:C14" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B2:C9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B2:C9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B10:C14" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23909,7 +23907,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{D049FEC6-3D25-4B64-99FE-3FFD7AA32BEA}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{3F107563-3415-4613-91F9-C195DA1F1DCA}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -23919,13 +23917,13 @@
     <col min="2" max="2" width="24.50390625" customWidth="1"/>
     <col min="3" max="3" width="18.50390625" customWidth="1"/>
     <col min="4" max="4" width="12.25390625" customWidth="1"/>
-    <col min="5" max="5" style="28" width="16.50390625" customWidth="1"/>
+    <col min="5" max="5" style="27" width="16.50390625" customWidth="1"/>
     <col min="6" max="6" width="11.00390625" customWidth="1"/>
     <col min="7" max="7" width="9.25390625" customWidth="1"/>
     <col min="8" max="8" width="10.125" customWidth="1"/>
-    <col min="9" max="9" style="28" width="20.375" customWidth="1"/>
-    <col min="10" max="10" style="28" width="11.125" customWidth="1"/>
-    <col min="12" max="12" style="27" width="14.00390625" customWidth="1"/>
+    <col min="9" max="9" style="27" width="20.375" customWidth="1"/>
+    <col min="10" max="10" style="27" width="11.125" customWidth="1"/>
+    <col min="12" max="12" style="26" width="14.00390625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="35.25" customHeight="1">
@@ -24497,7 +24495,7 @@
       <c r="J16" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="K16" s="29" t="s">
+      <c r="K16" s="25" t="s">
         <v>165</v>
       </c>
       <c r="L16" s="23" t="s">
@@ -24648,10 +24646,10 @@
       <c r="J20" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K20" s="26" t="s">
+      <c r="K20" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="L20" s="27" t="s">
+      <c r="L20" s="26" t="s">
         <v>176</v>
       </c>
     </row>
@@ -24683,10 +24681,10 @@
       <c r="I21" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="J21" s="28">
+      <c r="J21" s="27">
         <v>0</v>
       </c>
-      <c r="L21" s="27" t="s">
+      <c r="L21" s="26" t="s">
         <v>178</v>
       </c>
     </row>
@@ -24718,10 +24716,10 @@
       <c r="I22" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="J22" s="28">
+      <c r="J22" s="27">
         <v>1</v>
       </c>
-      <c r="L22" s="27" t="s">
+      <c r="L22" s="26" t="s">
         <v>180</v>
       </c>
     </row>
@@ -24736,7 +24734,7 @@
       <c r="D23" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="E23" s="28" t="s">
+      <c r="E23" s="27" t="s">
         <v>129</v>
       </c>
     </row>
@@ -24765,7 +24763,7 @@
       <c r="I24" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="J24" s="28" t="s">
+      <c r="J24" s="27" t="s">
         <v>129</v>
       </c>
     </row>
@@ -24794,7 +24792,7 @@
       <c r="I25" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="J25" s="28" t="s">
+      <c r="J25" s="27" t="s">
         <v>129</v>
       </c>
     </row>
@@ -34655,8 +34653,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
+    <dataValidation allowBlank="1" errorStyle="warning" showErrorMessage="1" showInputMessage="1" sqref="B2"/>
     <dataValidation allowBlank="1" errorStyle="warning" showErrorMessage="1" showInputMessage="1" sqref="B3:B20"/>
-    <dataValidation allowBlank="1" errorStyle="warning" showErrorMessage="1" showInputMessage="1" sqref="B2"/>
   </dataValidations>
   <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -34673,7 +34671,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{5C340BD2-F148-4328-A95B-C7A62EF7266F}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{D09FB2E6-E762-43BC-AD0F-EFF9E81590C8}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -34705,7 +34703,7 @@
       <c r="E1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="28" t="s">
         <v>186</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -43231,10 +43229,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A23" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A2:A9" type="list">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="A10:A23" type="list">
       <formula1>"S,N"</formula1>
     </dataValidation>
   </dataValidations>
